--- a/BeatnotePostHotCell/Jun12,2026/Fit_ResultJun12.xlsx
+++ b/BeatnotePostHotCell/Jun12,2026/Fit_ResultJun12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun12,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun12,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80897364-6FED-4420-AB8D-BF15F00A081D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC353025-881D-4C25-9D8B-9A589CA215EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -180,22 +180,13 @@
   </si>
   <si>
     <t>Jun12,2026+5-27-44PM</t>
-  </si>
-  <si>
-    <t>Jun12,2026+2-24-42PM</t>
-  </si>
-  <si>
-    <t>Jun12,2026+2-36-07PM</t>
-  </si>
-  <si>
-    <t>Jun12,2026+4-16-31PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,9 +558,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:Z37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -646,7 +637,7 @@
       <c r="R2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -671,7 +662,7 @@
       <c r="H3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -696,7 +687,7 @@
       <c r="H4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -721,7 +712,7 @@
       <c r="H5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -746,7 +737,7 @@
       <c r="H6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -771,7 +762,7 @@
       <c r="H7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -796,7 +787,7 @@
       <c r="H8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -821,7 +812,7 @@
       <c r="H9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -846,7 +837,7 @@
       <c r="H10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -872,7 +863,7 @@
       <c r="R11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -898,7 +889,7 @@
       <c r="R12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -924,7 +915,7 @@
       <c r="R13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -950,7 +941,7 @@
       <c r="R14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -976,7 +967,7 @@
       <c r="R15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -1002,7 +993,7 @@
       <c r="R16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,7 +1018,7 @@
       <c r="H17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1052,7 +1043,7 @@
       <c r="H18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1077,7 +1068,7 @@
       <c r="H19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1101,7 +1092,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -1125,7 +1116,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1148,7 +1139,7 @@
         <v>2.2873004957014299E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1171,7 +1162,7 @@
         <v>2.2873004957636202E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1194,7 +1185,7 @@
         <v>2.28730049587735E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="42.75">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1217,7 +1208,7 @@
         <v>2.28730049570209E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="42.75">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -1240,7 +1231,7 @@
         <v>2.2873004957014698E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="42.75">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -1263,7 +1254,7 @@
         <v>2.2873004957071502E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="42.75">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1286,7 +1277,7 @@
         <v>2.2873004957033299E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="42.75">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -1309,7 +1300,7 @@
         <v>2.5643901895510998E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="42.75">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -1332,7 +1323,7 @@
         <v>3.01446614133227E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="42.75">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1355,7 +1346,7 @@
         <v>2.2873004963648402E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="42.75">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1378,7 +1369,7 @@
         <v>2.2873004957052602E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="42.75">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -1401,7 +1392,7 @@
         <v>2.2873004957091399E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="42.75">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -1424,7 +1415,7 @@
         <v>2.28730049570141E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="42.75">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
@@ -1447,7 +1438,7 @@
         <v>2.2873004957170802E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="42.75">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
@@ -1470,7 +1461,7 @@
         <v>2.2873005006713801E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="42.75">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
@@ -1500,10 +1491,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
-  <dimension ref="A1:AA40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA41"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,12 +1545,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>0.22378459935658199</v>
+        <v>0.174179408135331</v>
       </c>
       <c r="C2" s="1">
         <v>1.5308853682119801</v>
@@ -1571,21 +1562,21 @@
         <v>-1.4730632613347501E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>3.2337195953002702</v>
+        <v>3.17252022203657</v>
       </c>
       <c r="G2" s="1">
-        <v>39.791523432233603</v>
+        <v>39.773020404490097</v>
       </c>
       <c r="H2" s="1">
-        <v>1.0389105359637899E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.6982894487302999E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1">
-        <v>0.228434718604688</v>
+        <v>0.177774925130529</v>
       </c>
       <c r="C3" s="1">
         <v>1.5312979761113501</v>
@@ -1597,21 +1588,21 @@
         <v>-1.9221981306232901E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>3.4739649759789</v>
+        <v>3.4127982868106099</v>
       </c>
       <c r="G3" s="1">
-        <v>41.821386871588999</v>
+        <v>41.823689063281201</v>
       </c>
       <c r="H3" s="1">
-        <v>1.0674036736176801E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.1887984879802202E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1">
-        <v>0.221372998488612</v>
+        <v>0.17240658415385299</v>
       </c>
       <c r="C4" s="1">
         <v>1.5300084075613001</v>
@@ -1623,21 +1614,21 @@
         <v>-1.4210427169117199E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.9764195028740299</v>
+        <v>2.9152427547995998</v>
       </c>
       <c r="G4" s="1">
-        <v>39.851480194995801</v>
+        <v>39.851480656806203</v>
       </c>
       <c r="H4" s="1">
-        <v>5.82913644273845E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8262388449346403E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="1">
-        <v>0.225975457594905</v>
+        <v>0.17600471089717301</v>
       </c>
       <c r="C5" s="1">
         <v>1.53232908320922</v>
@@ -1649,21 +1640,21 @@
         <v>-9.1476864557594396E-5</v>
       </c>
       <c r="F5" s="1">
-        <v>2.4884881244560701</v>
+        <v>2.42728517611426</v>
       </c>
       <c r="G5" s="1">
-        <v>39.918306408187902</v>
+        <v>40.095250935771503</v>
       </c>
       <c r="H5" s="1">
-        <v>6.3233624745193898E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8274724204530599E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="1">
-        <v>0.225216837741747</v>
+        <v>0.17541168833131099</v>
       </c>
       <c r="C6" s="1">
         <v>1.53228541521088</v>
@@ -1675,21 +1666,21 @@
         <v>-1.7677032494991499E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>2.2229690310837098</v>
+        <v>2.1617640215461602</v>
       </c>
       <c r="G6" s="1">
-        <v>39.879336578116899</v>
+        <v>39.962704595254202</v>
       </c>
       <c r="H6" s="1">
-        <v>5.9718548469899705E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8754815884245397E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1">
-        <v>0.229746279532067</v>
+        <v>0.178859466811089</v>
       </c>
       <c r="C7" s="1">
         <v>1.53315709687793</v>
@@ -1701,21 +1692,21 @@
         <v>-1.245154524299E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>1.97425632697381</v>
+        <v>1.9130805000823099</v>
       </c>
       <c r="G7" s="1">
-        <v>41.887897837475201</v>
+        <v>41.886895933231898</v>
       </c>
       <c r="H7" s="1">
-        <v>1.01324704629133E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.6843876076138605E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1">
-        <v>0.22722518963626401</v>
+        <v>0.17693051626013501</v>
       </c>
       <c r="C8" s="1">
         <v>1.5326139473275799</v>
@@ -1727,21 +1718,21 @@
         <v>-1.3236729401283601E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>1.9721619645221899</v>
+        <v>1.9109664091715299</v>
       </c>
       <c r="G8" s="1">
-        <v>41.876112059805102</v>
+        <v>41.714393804679801</v>
       </c>
       <c r="H8" s="1">
-        <v>1.1480888688318899E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0761447084690599E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="1">
-        <v>0.222965184868961</v>
+        <v>0.17354864156647201</v>
       </c>
       <c r="C9" s="1">
         <v>1.53190196624852</v>
@@ -1753,21 +1744,21 @@
         <v>-1.4876824659201501E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>1.9843088047886901</v>
+        <v>1.92312916143957</v>
       </c>
       <c r="G9" s="1">
-        <v>39.910959506280903</v>
+        <v>39.901918465841099</v>
       </c>
       <c r="H9" s="1">
-        <v>9.9637860886012206E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.6328716621812795E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="1">
-        <v>0.22898718060617901</v>
+        <v>0.17834649689539001</v>
       </c>
       <c r="C10" s="1">
         <v>1.53242990764706</v>
@@ -1779,21 +1770,21 @@
         <v>-1.6812824133017801E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>1.9738253341788501</v>
+        <v>1.9126750019390499</v>
       </c>
       <c r="G10" s="1">
-        <v>41.893144213585302</v>
+        <v>41.893228704427202</v>
       </c>
       <c r="H10" s="1">
-        <v>1.1348246707409101E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.15715383261446E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="1">
-        <v>0.22580668748875701</v>
+        <v>0.17586320937466099</v>
       </c>
       <c r="C11" s="1">
         <v>1.53241753658764</v>
@@ -1805,21 +1796,21 @@
         <v>-8.5964195986242405E-5</v>
       </c>
       <c r="F11" s="1">
-        <v>1.98377806202258</v>
+        <v>1.9225867774680601</v>
       </c>
       <c r="G11" s="1">
-        <v>39.945344084032101</v>
+        <v>39.957275780743998</v>
       </c>
       <c r="H11" s="1">
-        <v>5.8304357058488402E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8357793810527797E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="1">
-        <v>0.231594890582631</v>
+        <v>0.180271615500876</v>
       </c>
       <c r="C12" s="1">
         <v>1.5311333943744501</v>
@@ -1831,21 +1822,21 @@
         <v>-2.0341123982904599E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>1.9735921892686901</v>
+        <v>1.9124279158961599</v>
       </c>
       <c r="G12" s="1">
-        <v>41.945772760564097</v>
+        <v>41.942343759648402</v>
       </c>
       <c r="H12" s="1">
-        <v>9.3767408282896395E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.1303701500430496E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="1">
-        <v>0.224583618990919</v>
+        <v>0.17487871734820501</v>
       </c>
       <c r="C13" s="1">
         <v>1.5308838148747099</v>
@@ -1857,21 +1848,21 @@
         <v>-7.5209466174799004E-5</v>
       </c>
       <c r="F13" s="1">
-        <v>1.9849697898112699</v>
+        <v>1.9237910957451501</v>
       </c>
       <c r="G13" s="1">
-        <v>39.9968395137725</v>
+        <v>40.025800010197699</v>
       </c>
       <c r="H13" s="1">
-        <v>7.0180955526698697E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7984521850562305E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="1">
-        <v>0.23249128317182099</v>
+        <v>0.18107037027506301</v>
       </c>
       <c r="C14" s="1">
         <v>1.52962234816248</v>
@@ -1883,21 +1874,21 @@
         <v>-1.5058541630539701E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>1.98325564465251</v>
+        <v>1.9221067214408201</v>
       </c>
       <c r="G14" s="1">
-        <v>41.980001527958798</v>
+        <v>41.979281635377099</v>
       </c>
       <c r="H14" s="1">
-        <v>1.13793824393878E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1345054414932101E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="1">
-        <v>0.23073510515949899</v>
+        <v>0.17968547629579501</v>
       </c>
       <c r="C15" s="1">
         <v>1.53106067017592</v>
@@ -1909,21 +1900,21 @@
         <v>-2.1715276437974499E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>1.98031722537709</v>
+        <v>1.91916224156611</v>
       </c>
       <c r="G15" s="1">
-        <v>41.990921595394397</v>
+        <v>41.9886434536335</v>
       </c>
       <c r="H15" s="1">
-        <v>1.1570467944010199E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1028472058214501E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="1">
-        <v>0.229179326874075</v>
+        <v>0.17831650497979901</v>
       </c>
       <c r="C16" s="1">
         <v>1.53089412766376</v>
@@ -1935,21 +1926,21 @@
         <v>-2.3564983085827299E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>1.9728755054848499</v>
+        <v>1.9117124482142001</v>
       </c>
       <c r="G16" s="1">
-        <v>42.020723304815597</v>
+        <v>42.020632370918896</v>
       </c>
       <c r="H16" s="1">
-        <v>1.15526239480591E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8222260744936595E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>0.226024665246639</v>
+        <v>0.17606881780824499</v>
       </c>
       <c r="C17" s="1">
         <v>1.53026526973184</v>
@@ -1961,21 +1952,21 @@
         <v>-1.2010773074683301E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>1.98156219988524</v>
+        <v>1.9203766794446999</v>
       </c>
       <c r="G17" s="1">
-        <v>40.024487620385997</v>
+        <v>40.210780861633403</v>
       </c>
       <c r="H17" s="1">
-        <v>5.8066886276125003E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.2734814690627405E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>0.22988414195496401</v>
+        <v>0.179066023936296</v>
       </c>
       <c r="C18" s="1">
         <v>1.5293835766219399</v>
@@ -1987,21 +1978,21 @@
         <v>-2.0756668759662399E-4</v>
       </c>
       <c r="F18" s="1">
-        <v>1.97738908125935</v>
+        <v>1.9162340559820099</v>
       </c>
       <c r="G18" s="1">
-        <v>41.830047953171999</v>
+        <v>42.006755626816997</v>
       </c>
       <c r="H18" s="1">
-        <v>1.10061796198996E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.11644730979738E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>0.22795719930278499</v>
+        <v>0.177536328461042</v>
       </c>
       <c r="C19" s="1">
         <v>1.52936485200919</v>
@@ -2013,560 +2004,512 @@
         <v>-1.75405995161395E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>2.2304340763911799</v>
+        <v>2.1692514038077699</v>
       </c>
       <c r="G19" s="1">
-        <v>39.992574194716198</v>
+        <v>39.992451015654296</v>
       </c>
       <c r="H19" s="1">
-        <v>5.8433675843783605E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693550205703E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
-        <v>0.22143350081607599</v>
+        <v>0.17700590462459101</v>
       </c>
       <c r="C20" s="1">
-        <v>1.5299598084101</v>
+        <v>1.5303196378816999</v>
       </c>
       <c r="D20" s="1">
-        <v>9.3239342272600795E-4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>-8.54930520240561E-5</v>
+        <v>1.0637378730473999E-3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-1.2476798703879699E-4</v>
       </c>
       <c r="F20" s="1">
-        <v>1.97629611782367</v>
+        <v>1.9142266251567699</v>
       </c>
       <c r="G20" s="1">
-        <v>40.052778982587597</v>
+        <v>40.064619297401102</v>
       </c>
       <c r="H20" s="1">
-        <v>5.7857693471159905E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.0489575317797196E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1">
-        <v>0.219629412560333</v>
+        <v>0.176845695868282</v>
       </c>
       <c r="C21" s="1">
-        <v>1.52992762784195</v>
+        <v>1.52913290718884</v>
       </c>
       <c r="D21" s="1">
-        <v>1.08621348898894E-3</v>
+        <v>1.67350953807705E-3</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.21331267517151E-4</v>
+        <v>-2.04747724248948E-4</v>
       </c>
       <c r="F21" s="1">
-        <v>1.9789929383007201</v>
+        <v>2.3755851516306201</v>
       </c>
       <c r="G21" s="1">
-        <v>40.060175431242698</v>
+        <v>40.055530090592598</v>
       </c>
       <c r="H21" s="1">
-        <v>5.8933463387886005E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693440737995E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1">
-        <v>0.227267035209756</v>
+        <v>0.17772123501191101</v>
       </c>
       <c r="C22" s="1">
-        <v>1.5303196378816999</v>
+        <v>1.5299700841335</v>
       </c>
       <c r="D22" s="1">
-        <v>1.0637378730473999E-3</v>
+        <v>1.3864791450600301E-3</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.2476798703879699E-4</v>
+        <v>-1.7472530804288301E-4</v>
       </c>
       <c r="F22" s="1">
-        <v>1.9753814468986299</v>
+        <v>1.91110525328321</v>
       </c>
       <c r="G22" s="1">
-        <v>40.064594280269397</v>
+        <v>40.063860640658</v>
       </c>
       <c r="H22" s="1">
-        <v>5.7857821900775697E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8014980563106703E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>0.22728875634974799</v>
+        <v>0.17485108835940399</v>
       </c>
       <c r="C23" s="1">
-        <v>1.5295401370291499</v>
+        <v>1.5296439847599399</v>
       </c>
       <c r="D23" s="1">
-        <v>1.5047131230324299E-3</v>
+        <v>1.3918639819668001E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>-1.89297665214606E-4</v>
+        <v>-1.5548016664387101E-4</v>
       </c>
       <c r="F23" s="1">
-        <v>2.2255491596804098</v>
+        <v>2.1717507920886399</v>
       </c>
       <c r="G23" s="1">
-        <v>40.055802922936302</v>
+        <v>40.113174896797297</v>
       </c>
       <c r="H23" s="1">
-        <v>5.8254215467203399E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7892495918432699E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1">
-        <v>0.22819660608103401</v>
+        <v>0.174086444253885</v>
       </c>
       <c r="C24" s="1">
-        <v>1.5299700841335</v>
+        <v>1.52974859403824</v>
       </c>
       <c r="D24" s="1">
-        <v>1.3864791450600301E-3</v>
+        <v>1.20215945066828E-3</v>
       </c>
       <c r="E24" s="1">
-        <v>-1.7472530804288301E-4</v>
+        <v>-1.3870797467815699E-4</v>
       </c>
       <c r="F24" s="1">
-        <v>1.97225390592434</v>
+        <v>1.9202988966301999</v>
       </c>
       <c r="G24" s="1">
-        <v>40.063352898362297</v>
+        <v>40.045969723337301</v>
       </c>
       <c r="H24" s="1">
-        <v>5.78597593425109E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1998837509750196E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1">
-        <v>0.22449918198189101</v>
+        <v>0.17721978032439201</v>
       </c>
       <c r="C25" s="1">
-        <v>1.5296439847599399</v>
+        <v>1.53100332291526</v>
       </c>
       <c r="D25" s="1">
-        <v>1.3918639819668001E-3</v>
+        <v>1.1518415444654001E-3</v>
       </c>
       <c r="E25" s="1">
-        <v>-1.5548016664387101E-4</v>
+        <v>-1.8871858153473E-4</v>
       </c>
       <c r="F25" s="1">
-        <v>2.2329420982030399</v>
+        <v>1.12754339814528</v>
       </c>
       <c r="G25" s="1">
-        <v>40.066986822769998</v>
+        <v>42.057659492809101</v>
       </c>
       <c r="H25" s="1">
-        <v>5.7857696129767701E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1567466284181701E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1">
-        <v>0.22352994908158599</v>
+        <v>0.177247013055988</v>
       </c>
       <c r="C26" s="1">
-        <v>1.52974859403824</v>
+        <v>1.53118369974652</v>
       </c>
       <c r="D26" s="1">
-        <v>1.20215945066828E-3</v>
-      </c>
-      <c r="E26" s="1">
-        <v>-1.3870797467815699E-4</v>
+        <v>9.62259587421309E-4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-7.4325631212104006E-5</v>
       </c>
       <c r="F26" s="1">
-        <v>1.9814988741499899</v>
+        <v>1.90848883088794</v>
       </c>
       <c r="G26" s="1">
-        <v>40.074969175073697</v>
+        <v>40.097388873776403</v>
       </c>
       <c r="H26" s="1">
-        <v>7.1816035514961005E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7998258605507496E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="42.75">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1">
-        <v>0.22753327784977401</v>
+        <v>0.17554660297643901</v>
       </c>
       <c r="C27" s="1">
-        <v>1.53100332291526</v>
+        <v>1.53121618681344</v>
       </c>
       <c r="D27" s="1">
-        <v>1.1518415444654001E-3</v>
-      </c>
-      <c r="E27" s="1">
-        <v>-1.8871858153473E-4</v>
+        <v>9.7693402926031904E-4</v>
+      </c>
+      <c r="E27" s="2">
+        <v>-7.5764728044511507E-5</v>
       </c>
       <c r="F27" s="1">
-        <v>1.18871494672916</v>
+        <v>1.92517053593135</v>
       </c>
       <c r="G27" s="1">
-        <v>42.0565925432781</v>
+        <v>40.1067215020107</v>
       </c>
       <c r="H27" s="1">
-        <v>1.12307200542073E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.67160087607811E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="42.75">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1">
-        <v>0.22784419865740199</v>
+        <v>0.176832773520505</v>
       </c>
       <c r="C28" s="1">
-        <v>1.53118369974652</v>
+        <v>1.5311195965834199</v>
       </c>
       <c r="D28" s="1">
-        <v>9.62259587421309E-4</v>
-      </c>
-      <c r="E28" s="2">
-        <v>-7.4325631212104006E-5</v>
+        <v>1.23517474076262E-3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>-1.2630439122957799E-4</v>
       </c>
       <c r="F28" s="1">
-        <v>1.9696700915394401</v>
+        <v>1.92575716143548</v>
       </c>
       <c r="G28" s="1">
-        <v>41.700262768858899</v>
+        <v>41.526342998261001</v>
       </c>
       <c r="H28" s="1">
-        <v>6.1495983890116998E-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.15165859817244E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="42.75">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1">
-        <v>0.225433003733543</v>
+        <v>0.178312428161159</v>
       </c>
       <c r="C29" s="1">
-        <v>1.53121618681344</v>
+        <v>1.53055273774849</v>
       </c>
       <c r="D29" s="1">
-        <v>9.7693402926031904E-4</v>
-      </c>
-      <c r="E29" s="2">
-        <v>-7.5764728044511507E-5</v>
+        <v>1.2311895034853801E-3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>-1.2680005223687801E-4</v>
       </c>
       <c r="F29" s="1">
-        <v>1.9863311481369299</v>
+        <v>1.9280548928679899</v>
       </c>
       <c r="G29" s="1">
-        <v>40.111452957311897</v>
+        <v>42.018834455590998</v>
       </c>
       <c r="H29" s="1">
-        <v>8.4285494913599395E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.13137344440978E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="42.75">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1">
-        <v>0.22712348211729699</v>
+        <v>0.17923862445315999</v>
       </c>
       <c r="C30" s="1">
-        <v>1.5311195965834199</v>
+        <v>1.5292869185215801</v>
       </c>
       <c r="D30" s="1">
-        <v>1.23517474076262E-3</v>
+        <v>1.14791509378189E-3</v>
       </c>
       <c r="E30" s="1">
-        <v>-1.2630439122957799E-4</v>
+        <v>-1.14140056792596E-4</v>
       </c>
       <c r="F30" s="1">
-        <v>1.9869296021951699</v>
+        <v>1.87434410374409</v>
       </c>
       <c r="G30" s="1">
-        <v>42.034796065630701</v>
+        <v>40.472769180464198</v>
       </c>
       <c r="H30" s="1">
-        <v>1.1418544843247E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7858710034960903E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1">
-        <v>0.22124832901956601</v>
+        <v>0.17704529946634301</v>
       </c>
       <c r="C31" s="1">
-        <v>1.5299830287128899</v>
+        <v>1.5294640131695201</v>
       </c>
       <c r="D31" s="1">
-        <v>1.48866731963536E-3</v>
+        <v>1.45572135225585E-3</v>
       </c>
       <c r="E31" s="1">
-        <v>-1.48326245234397E-4</v>
+        <v>-1.66093874133778E-4</v>
       </c>
       <c r="F31" s="1">
-        <v>2.2412113882715601</v>
+        <v>1.91776123053748</v>
       </c>
       <c r="G31" s="1">
-        <v>40.063236562113197</v>
+        <v>42.059854022566398</v>
       </c>
       <c r="H31" s="1">
-        <v>5.7857693431832098E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1103002714711299E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1">
-        <v>0.22894109101944199</v>
+        <v>0.17678671405309901</v>
       </c>
       <c r="C32" s="1">
-        <v>1.53055273774849</v>
+        <v>1.53011326910762</v>
       </c>
       <c r="D32" s="1">
-        <v>1.2311895034853801E-3</v>
+        <v>1.3728333011140601E-3</v>
       </c>
       <c r="E32" s="1">
-        <v>-1.2680005223687801E-4</v>
+        <v>-1.83107742573945E-4</v>
       </c>
       <c r="F32" s="1">
-        <v>1.98923345740209</v>
+        <v>1.67185544040621</v>
       </c>
       <c r="G32" s="1">
-        <v>42.007148021399502</v>
+        <v>40.102050332876999</v>
       </c>
       <c r="H32" s="1">
-        <v>1.12160678636843E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.2469284886941296E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="42.75">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1">
-        <v>0.23027592968354901</v>
+        <v>0.173286761817802</v>
       </c>
       <c r="C33" s="1">
-        <v>1.5292869185215801</v>
+        <v>1.5307370748707501</v>
       </c>
       <c r="D33" s="1">
-        <v>1.14791509378189E-3</v>
+        <v>1.33309418889631E-3</v>
       </c>
       <c r="E33" s="1">
-        <v>-1.14140056792596E-4</v>
+        <v>-1.6811678651033101E-4</v>
       </c>
       <c r="F33" s="1">
-        <v>1.9355108428669201</v>
+        <v>1.87469687306584</v>
       </c>
       <c r="G33" s="1">
-        <v>41.257487857538301</v>
+        <v>40.129108617087198</v>
       </c>
       <c r="H33" s="1">
-        <v>6.14147096243569E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9508077940235895E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="42.75">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1">
-        <v>0.22733899516780401</v>
+        <v>0.17732355138347</v>
       </c>
       <c r="C34" s="1">
-        <v>1.5294640131695201</v>
+        <v>1.5313394094989701</v>
       </c>
       <c r="D34" s="1">
-        <v>1.45572135225585E-3</v>
-      </c>
-      <c r="E34" s="1">
-        <v>-1.66093874133778E-4</v>
+        <v>8.0019674689308501E-4</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-6.9554465067924498E-5</v>
       </c>
       <c r="F34" s="1">
-        <v>1.9789510459483699</v>
+        <v>1.66253844631238</v>
       </c>
       <c r="G34" s="1">
-        <v>42.064451529376001</v>
+        <v>40.127372097992399</v>
       </c>
       <c r="H34" s="1">
-        <v>1.15715384144877E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9474388824718599E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="42.75">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1">
-        <v>0.22718964047891599</v>
+        <v>0.17497871224561701</v>
       </c>
       <c r="C35" s="1">
-        <v>1.53011326910762</v>
+        <v>1.53108589597578</v>
       </c>
       <c r="D35" s="1">
-        <v>1.3728333011140601E-3</v>
+        <v>1.0421717926196001E-3</v>
       </c>
       <c r="E35" s="1">
-        <v>-1.83107742573945E-4</v>
+        <v>-1.2458950256210601E-4</v>
       </c>
       <c r="F35" s="1">
-        <v>1.73304300210365</v>
+        <v>1.8806113197741099</v>
       </c>
       <c r="G35" s="1">
-        <v>41.086128135192801</v>
+        <v>40.138911990128797</v>
       </c>
       <c r="H35" s="1">
-        <v>7.5216229704962504E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7857693432355605E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="42.75">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1">
-        <v>0.22249606599096799</v>
+        <v>0.17569336443192901</v>
       </c>
       <c r="C36" s="1">
-        <v>1.5307370748707501</v>
+        <v>1.53063980884305</v>
       </c>
       <c r="D36" s="1">
-        <v>1.33309418889631E-3</v>
-      </c>
-      <c r="E36" s="1">
-        <v>-1.6811678651033101E-4</v>
+        <v>6.9741296514191898E-4</v>
+      </c>
+      <c r="E36" s="2">
+        <v>-2.51340647600401E-6</v>
       </c>
       <c r="F36" s="1">
-        <v>1.93588875906647</v>
+        <v>1.9157743648724499</v>
       </c>
       <c r="G36" s="1">
-        <v>40.122329148698903</v>
+        <v>40.282455241001699</v>
       </c>
       <c r="H36" s="1">
-        <v>5.78577500403179E-4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7936444897464898E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="42.75">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1">
-        <v>0.22770140189949001</v>
+        <v>0.17739676585251099</v>
       </c>
       <c r="C37" s="1">
-        <v>1.5313394094989701</v>
+        <v>1.53216973654111</v>
       </c>
       <c r="D37" s="1">
-        <v>8.0019674689308501E-4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>-6.9554465067924498E-5</v>
+        <v>1.24202845404689E-3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>-1.40494536997847E-4</v>
       </c>
       <c r="F37" s="1">
-        <v>1.7237018785728799</v>
+        <v>1.8772489807508901</v>
       </c>
       <c r="G37" s="1">
-        <v>40.282937641447198</v>
+        <v>40.115441746558297</v>
       </c>
       <c r="H37" s="1">
-        <v>5.8017222708433105E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.22467693879523801</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.53108589597578</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1.0421717926196001E-3</v>
-      </c>
-      <c r="E38" s="1">
-        <v>-1.2458950256210601E-4</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1.94177797960933</v>
-      </c>
-      <c r="G38" s="1">
-        <v>40.138911990304699</v>
-      </c>
-      <c r="H38" s="1">
-        <v>5.7857693431690902E-4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.22590951148508701</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1.53063980884305</v>
-      </c>
-      <c r="D39" s="1">
-        <v>6.9741296514191898E-4</v>
-      </c>
-      <c r="E39" s="2">
-        <v>-2.51340647600401E-6</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1.9769693399464601</v>
-      </c>
-      <c r="G39" s="1">
-        <v>42.137570344128697</v>
-      </c>
-      <c r="H39" s="1">
-        <v>6.8101297652824601E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.22795873224990801</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1.53216973654111</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1.24202845404689E-3</v>
-      </c>
-      <c r="E40" s="1">
-        <v>-1.40494536997847E-4</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1.9384346981673</v>
-      </c>
-      <c r="G40" s="1">
-        <v>41.305571978850203</v>
-      </c>
-      <c r="H40" s="1">
-        <v>5.8278836326500997E-4</v>
-      </c>
+        <v>5.7860852926031503E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2575,13 +2518,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2592,7 +2535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -2600,7 +2543,7 @@
         <v>13.881207281537201</v>
       </c>
       <c r="C2" s="1">
-        <v>0.22378459935658199</v>
+        <v>0.174179408135331</v>
       </c>
       <c r="F2">
         <v>894</v>
@@ -2608,8 +2551,9 @@
       <c r="G2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2617,7 +2561,7 @@
         <v>14.0895904209866</v>
       </c>
       <c r="C3" s="1">
-        <v>0.228434718604688</v>
+        <v>0.177774925130529</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -2628,10 +2572,11 @@
       </c>
       <c r="G3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.2270913305814001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17682018337838198</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2639,7 +2584,7 @@
         <v>13.781524940490501</v>
       </c>
       <c r="C4" s="1">
-        <v>0.221372998488612</v>
+        <v>0.17240658415385299</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -2650,10 +2595,11 @@
       </c>
       <c r="G4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>2.6733214476306636E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.0730475475276987E-3</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2661,7 +2607,7 @@
         <v>13.849983967959</v>
       </c>
       <c r="C5" s="1">
-        <v>0.225975457594905</v>
+        <v>0.17600471089717301</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -2672,10 +2618,11 @@
       </c>
       <c r="G5">
         <f>G4/G3/SQRT(COUNT(C2:C33))</f>
-        <v>2.0810170505754953E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.0725376913592122E-3</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -2683,10 +2630,11 @@
         <v>14.1045893865774</v>
       </c>
       <c r="C6" s="1">
-        <v>0.225216837741747</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17541168833131099</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -2694,10 +2642,11 @@
         <v>14.045243904631301</v>
       </c>
       <c r="C7" s="1">
-        <v>0.229746279532067</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.178859466811089</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -2705,10 +2654,11 @@
         <v>14.041948410297801</v>
       </c>
       <c r="C8" s="1">
-        <v>0.22722518963626401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17693051626013501</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -2716,10 +2666,11 @@
         <v>13.9314720937797</v>
       </c>
       <c r="C9" s="1">
-        <v>0.222965184868961</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17354864156647201</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -2727,10 +2678,11 @@
         <v>13.939302031872</v>
       </c>
       <c r="C10" s="1">
-        <v>0.22898718060617901</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17834649689539001</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -2738,10 +2690,11 @@
         <v>13.7686312681289</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22580668748875701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17586320937466099</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -2749,10 +2702,11 @@
         <v>13.860947786333201</v>
       </c>
       <c r="C12" s="1">
-        <v>0.231594890582631</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.180271615500876</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2760,10 +2714,11 @@
         <v>14.0288192886568</v>
       </c>
       <c r="C13" s="1">
-        <v>0.224583618990919</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17487871734820501</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -2771,10 +2726,11 @@
         <v>14.0564949797</v>
       </c>
       <c r="C14" s="1">
-        <v>0.23249128317182099</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.18107037027506301</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -2782,10 +2738,11 @@
         <v>13.967021506007001</v>
       </c>
       <c r="C15" s="1">
-        <v>0.23073510515949899</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17968547629579501</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -2793,10 +2750,11 @@
         <v>13.8984865800428</v>
       </c>
       <c r="C16" s="1">
-        <v>0.229179326874075</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17831650497979901</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -2804,10 +2762,11 @@
         <v>13.7709959964952</v>
       </c>
       <c r="C17" s="1">
-        <v>0.226024665246639</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17606881780824499</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -2815,10 +2774,11 @@
         <v>13.7843547051184</v>
       </c>
       <c r="C18" s="1">
-        <v>0.22988414195496401</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.179066023936296</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2826,10 +2786,11 @@
         <v>13.808475282008599</v>
       </c>
       <c r="C19" s="1">
-        <v>0.22795719930278499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.177536328461042</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="42.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -2837,10 +2798,11 @@
         <v>14.015153400719299</v>
       </c>
       <c r="C20" s="1">
-        <v>0.227267035209756</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17700590462459101</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="42.75">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -2848,10 +2810,11 @@
         <v>14.0254740862873</v>
       </c>
       <c r="C21" s="1">
-        <v>0.22728875634974799</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.176845695868282</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="42.75">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -2859,10 +2822,11 @@
         <v>13.9997618436749</v>
       </c>
       <c r="C22" s="1">
-        <v>0.22819660608103401</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17772123501191101</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="42.75">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -2870,10 +2834,11 @@
         <v>14.019342208389499</v>
       </c>
       <c r="C23" s="1">
-        <v>0.22449918198189101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17485108835940399</v>
+      </c>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="42.75">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -2881,10 +2846,11 @@
         <v>13.970695398759901</v>
       </c>
       <c r="C24" s="1">
-        <v>0.22352994908158599</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.174086444253885</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="42.75">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -2892,10 +2858,11 @@
         <v>13.907971630891801</v>
       </c>
       <c r="C25" s="1">
-        <v>0.22753327784977401</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17721978032439201</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="42.75">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2903,10 +2870,11 @@
         <v>13.8994236879669</v>
       </c>
       <c r="C26" s="1">
-        <v>0.22784419865740199</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.177247013055988</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="42.75">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -2914,10 +2882,11 @@
         <v>14.055169741167299</v>
       </c>
       <c r="C27" s="1">
-        <v>0.225433003733543</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17554660297643901</v>
+      </c>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="42.75">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -2925,10 +2894,11 @@
         <v>13.9142762890247</v>
       </c>
       <c r="C28" s="1">
-        <v>0.22712348211729699</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.176832773520505</v>
+      </c>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="42.75">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -2936,10 +2906,11 @@
         <v>13.841323444683701</v>
       </c>
       <c r="C29" s="1">
-        <v>0.22894109101944199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.178312428161159</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="42.75">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -2947,10 +2918,11 @@
         <v>13.804980095407201</v>
       </c>
       <c r="C30" s="1">
-        <v>0.23027592968354901</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17923862445315999</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="42.75">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -2958,10 +2930,11 @@
         <v>13.884446951227901</v>
       </c>
       <c r="C31" s="1">
-        <v>0.22733899516780401</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17704529946634301</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="42.75">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -2969,10 +2942,11 @@
         <v>13.963402223733601</v>
       </c>
       <c r="C32" s="1">
-        <v>0.22718964047891599</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17678671405309901</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="42.75">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -2980,10 +2954,11 @@
         <v>13.9597270287277</v>
       </c>
       <c r="C33" s="1">
-        <v>0.22249606599096799</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.173286761817802</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="42.75">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -2991,10 +2966,11 @@
         <v>13.946102058433601</v>
       </c>
       <c r="C34" s="1">
-        <v>0.22770140189949001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17732355138347</v>
+      </c>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="42.75">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
@@ -3002,10 +2978,11 @@
         <v>13.9823014618208</v>
       </c>
       <c r="C35" s="1">
-        <v>0.22467693879523801</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17497871224561701</v>
+      </c>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="42.75">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
@@ -3013,10 +2990,11 @@
         <v>13.749906400784599</v>
       </c>
       <c r="C36" s="1">
-        <v>0.22590951148508701</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>0.17569336443192901</v>
+      </c>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="42.75">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
@@ -3024,8 +3002,9 @@
         <v>13.720594247384501</v>
       </c>
       <c r="C37" s="1">
-        <v>0.22795873224990801</v>
-      </c>
+        <v>0.17739676585251099</v>
+      </c>
+      <c r="J37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
